--- a/questionnaire_templates/029_healthcare_m_a_assessment_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/029_healthcare_m_a_assessment_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-active'}</t>
+          <t>non-active</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Active'}</t>
+          <t>Non-Active</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_longer_active'}</t>
+          <t>no_longer_active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No Longer Active'}</t>
+          <t>No Longer Active</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'north_america'}</t>
+          <t>north_america</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'North America'}</t>
+          <t>North America</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'south_america'}</t>
+          <t>south_america</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'South America'}</t>
+          <t>South America</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'market_risk'}</t>
+          <t>market_risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Market Risk'}</t>
+          <t>Market Risk</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'financial_risk'}</t>
+          <t>financial_risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Financial Risk'}</t>
+          <t>Financial Risk</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'legal_risk'}</t>
+          <t>legal_risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Legal Risk'}</t>
+          <t>Legal Risk</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'consortium'}</t>
+          <t>consortium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Consortium'}</t>
+          <t>Consortium</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'discounted_cash_flow'}</t>
+          <t>discounted_cash_flow</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Discounted Cash Flow'}</t>
+          <t>Discounted Cash Flow</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'net_present_value'}</t>
+          <t>net_present_value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Net Present Value'}</t>
+          <t>Net Present Value</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cost_of_assets'}</t>
+          <t>cost_of_assets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cost of Assets'}</t>
+          <t>Cost of Assets</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'acquisition'}</t>
+          <t>acquisition</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Acquisition'}</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'merger'}</t>
+          <t>merger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Merger'}</t>
+          <t>Merger</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'valuation'}</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Valuation'}</t>
+          <t>Valuation</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>target_ownership_type_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
